--- a/public/sample_uploads/remittance_recon_call_719_icici.xlsx
+++ b/public/sample_uploads/remittance_recon_call_719_icici.xlsx
@@ -327,13 +327,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="66.0" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="14.3" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="15.400000000000002" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="64.9" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="77.0" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="19.8" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="16.5" min="6" max="6" bestFit="1" customWidth="1"/>
   </cols>
@@ -552,7 +552,7 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>TRFR FROM:NOBODY MATCHES ME</t>
+          <t>RTGS-HDFCR500000719 0010801-G-50100133674524-HDFC0000240</t>
         </is>
       </c>
       <c r="E12" s="0"/>
@@ -576,38 +576,1766 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>SGB/3101499/FUND 1/Transfer</t>
-        </is>
-      </c>
-      <c r="E13" s="0" t="n">
-        <v>1900000.0</v>
-      </c>
-      <c r="F13" s="0"/>
+          <t>RTGS-HDFCR500000719 0010802-H-00601100066619-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0" t="n">
+        <v>100000.0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="A14" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>S000719009</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>25/Feb/2025</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>RTGS-HDFCR500000719 0010803-I-50200007064902-HDFC0000240</t>
         </is>
       </c>
       <c r="E14" s="0"/>
       <c r="F14" s="0" t="n">
-        <v>1469650.0</v>
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>S000719010</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010804-J-50100035238824-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>S000719011</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010806-L-00142790000324-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>S000719012</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010807-M-50132010049181-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>S000719013</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010808-N-10324773718-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0" t="n">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>S000719014</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>TRFR FROM:O</t>
+        </is>
+      </c>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0" t="n">
+        <v>5000000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>S000719015</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010810-P-00602480038037-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0" t="n">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>S000719016</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010811-Q-50100225695725-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0" t="n">
+        <v>125000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>S000719017</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010812-R-50100263909150-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>S000719018</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010813-S-00601100058003-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>S000719019</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010814-T-50100190500177-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E24" s="0"/>
+      <c r="F24" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>S000719020</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010815-U-50100279243414-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>S000719021</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010816-V-50200039466179-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E26" s="0"/>
+      <c r="F26" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>S000719022</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010817-W-50100140518099-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E27" s="0"/>
+      <c r="F27" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>S000719023</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010818-X-02911610049610-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E28" s="0"/>
+      <c r="F28" s="0" t="n">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>S000719024</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010819-Y-50200033085962-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E29" s="0"/>
+      <c r="F29" s="0" t="n">
+        <v>3000000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>S000719025</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010820-Z-00600340080091-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0" t="n">
+        <v>2000000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>S000719026</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010821-AA-50100169434100-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>S000719027</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010822-AB-50100265170502-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E32" s="0"/>
+      <c r="F32" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>S000719028</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010823-AC-50100104765675-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E33" s="0"/>
+      <c r="F33" s="0" t="n">
+        <v>1500000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>S000719029</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010824-AD-00591050008474-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E34" s="0"/>
+      <c r="F34" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>S000719030</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010825-AE-50200062960056-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E35" s="0"/>
+      <c r="F35" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>S000719031</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010826-AF-50100452472153-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E36" s="0"/>
+      <c r="F36" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>S000719032</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010827-AG-15772030011954-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E37" s="0"/>
+      <c r="F37" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>S000719033</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010828-AH-05227630000193-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>S000719034</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010829-AI-50200042386031-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E39" s="0"/>
+      <c r="F39" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>S000719035</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010830-AJ-50100129316544-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E40" s="0"/>
+      <c r="F40" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>S000719036</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010831-AK-50100174601251-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E41" s="0"/>
+      <c r="F41" s="0" t="n">
+        <v>750000.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>S000719037</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010832-AL-50200024385240-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E42" s="0"/>
+      <c r="F42" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>S000719038</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010833-AM-50200026492711-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E43" s="0"/>
+      <c r="F43" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>S000719039</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010834-AN-15772030008891-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E44" s="0"/>
+      <c r="F44" s="0" t="n">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>S000719040</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010835-AO-15772030008909-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E45" s="0"/>
+      <c r="F45" s="0" t="n">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>S000719041</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010836-AP-61159199180-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E46" s="0"/>
+      <c r="F46" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>S000719042</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010837-AQ-50100334040562-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E47" s="0"/>
+      <c r="F47" s="0" t="n">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>S000719043</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010838-AR-50200019917741-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E48" s="0"/>
+      <c r="F48" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>S000719044</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010839-AS-02401300000354-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E49" s="0"/>
+      <c r="F49" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>S000719045</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010840-AT-000405071553-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E50" s="0"/>
+      <c r="F50" s="0" t="n">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>S000719046</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010841-AU-50100226072314-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E51" s="0"/>
+      <c r="F51" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>S000719047</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010842-AV-50100212286171-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E52" s="0"/>
+      <c r="F52" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>S000719048</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010843-AW-50100213461809-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>S000719049</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010844-AX-918010022821819-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E54" s="0"/>
+      <c r="F54" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>S000719050</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010845-AY-50100225371522-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E55" s="0"/>
+      <c r="F55" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>S000719051</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010846-AZ-4912642396-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E56" s="0"/>
+      <c r="F56" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>S000719052</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010847-BA-50200024323031-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E57" s="0"/>
+      <c r="F57" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>S000719053</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010848-BB-50200034109309-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>S000719054</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010849-BC-10503338670-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0" t="n">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>S000719055</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010850-BD-50100196328630-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>S000719056</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010851-BE-10050170172-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>S000719057</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010852-BF-10050170310-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>S000719058</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>TRFR FROM:BG</t>
+        </is>
+      </c>
+      <c r="E63" s="0"/>
+      <c r="F63" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>S000719059</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>TRFR FROM:BH</t>
+        </is>
+      </c>
+      <c r="E64" s="0"/>
+      <c r="F64" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>S000719060</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010855-BI-50200031714742-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E65" s="0"/>
+      <c r="F65" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>S000719061</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010856-BJ-50200032982656-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E66" s="0"/>
+      <c r="F66" s="0" t="n">
+        <v>195470.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>S000719062</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010857-BK-50200032841632-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E67" s="0"/>
+      <c r="F67" s="0" t="n">
+        <v>191680.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>S000719063</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010858-BL-50100269866900-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E68" s="0"/>
+      <c r="F68" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>S000719064</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010859-BM-1787411939-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E69" s="0"/>
+      <c r="F69" s="0" t="n">
+        <v>240400.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>S000719065</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010860-BN-001501005380-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E70" s="0"/>
+      <c r="F70" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>S000719066</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010861-BO-50100201521237-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E71" s="0"/>
+      <c r="F71" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>S000719067</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010862-BP-50100090651508-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E72" s="0"/>
+      <c r="F72" s="0" t="n">
+        <v>7000268.51</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>S000719068</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010863-BQ-50100293012215-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E73" s="0"/>
+      <c r="F73" s="0" t="n">
+        <v>2360290.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>S000719069</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010864-BR-004103000025133-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E74" s="0"/>
+      <c r="F74" s="0" t="n">
+        <v>1888230.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>S000719070</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010865-BS-602320013480-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E75" s="0"/>
+      <c r="F75" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>S000719071</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010866-ARUNGUPTAHOLDING-3338880980-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E76" s="0"/>
+      <c r="F76" s="0" t="n">
+        <v>863500.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>S000719072</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010867-A-50100033849984-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E77" s="0"/>
+      <c r="F77" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>S000719073</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010868-ARUNGUPTAHOLDING-3388000182-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E78" s="0"/>
+      <c r="F78" s="0" t="n">
+        <v>600000.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>S000719074</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010869-INVESTOR11-2346898808-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E79" s="0"/>
+      <c r="F79" s="0" t="n">
+        <v>10000.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>S000719075</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0010870-ARUNGUPTAHOLDING-3338880980-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E80" s="0"/>
+      <c r="F80" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>S000719076</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t>TRFR FROM:AWESOME ACCOUNTING</t>
+        </is>
+      </c>
+      <c r="E81" s="0"/>
+      <c r="F81" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>S000719077</t>
+        </is>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t>RTGS-HDFCR500000719 0013796-ARUNGUPTAHOLDING-3338880980-HDFC0000240</t>
+        </is>
+      </c>
+      <c r="E82" s="0"/>
+      <c r="F82" s="0" t="n">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>S000719078</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t>TRFR FROM:AAA</t>
+        </is>
+      </c>
+      <c r="E83" s="0"/>
+      <c r="F83" s="0" t="n">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t>S000719079</t>
+        </is>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t>TRFR FROM:NOBODY MATCHES ME</t>
+        </is>
+      </c>
+      <c r="E84" s="0"/>
+      <c r="F84" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>S000719080</t>
+        </is>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>25/Feb/2025</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t>SGB/3101499/FUND 1/Transfer</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="n">
+        <v>1900000.0</v>
+      </c>
+      <c r="F85" s="0"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E86" s="0"/>
+      <c r="F86" s="0" t="n">
+        <v>37794488.51</v>
       </c>
     </row>
   </sheetData>
